--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260803.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>11,600,878</t>
+          <t>414,604,589</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>414,604,589</t>
+          <t>11,600,878</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>215,279,309</t>
+          <t>262,268,703</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>262,268,703</t>
+          <t>215,279,309</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,195,140</t>
+          <t>1,334,660</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,334,660</t>
+          <t>2,195,140</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
